--- a/artfynd/A 32098-2023 artfynd.xlsx
+++ b/artfynd/A 32098-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135999569</v>
       </c>
       <c r="B2" t="n">
-        <v>90448</v>
+        <v>90450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135999389</v>
       </c>
       <c r="B3" t="n">
-        <v>89242</v>
+        <v>89244</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
